--- a/output/pdf_financials_xlsx/ASTL.xlsx
+++ b/output/pdf_financials_xlsx/ASTL.xlsx
@@ -1452,10 +1452,10 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>21.2</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>915.3</v>
       </c>
       <c r="E34" s="1" t="inlineStr">
         <is>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>266.9</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>77.5</v>
       </c>
     </row>
     <row r="35">
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>21.2</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>915.3</v>
       </c>
       <c r="E36" s="1" t="inlineStr">
         <is>
@@ -1521,10 +1521,10 @@
         </is>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>266.9</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>77.5</v>
       </c>
     </row>
     <row r="37">
@@ -1858,10 +1858,10 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>568.2</v>
+        <v>547</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1514.2</v>
+        <v>598.9</v>
       </c>
       <c r="E48" s="1" t="inlineStr">
         <is>
@@ -1869,10 +1869,10 @@
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>399.6</v>
+        <v>132.7</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>320.4</v>
+        <v>242.9</v>
       </c>
     </row>
     <row r="49">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
